--- a/food_beverage_order_forms/026_organic_product_delivery_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/026_organic_product_delivery_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>product_select</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>1. Product</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>2. Delivery Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>3. Delivery Time</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>4. Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>5. Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>6. Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>7. Note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>select_product</t>
+          <t>select_product_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select Product</t>
+          <t>8. Select Another Product</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>select_product_2</t>
+          <t>select_product_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select Another Product</t>
+          <t>9. Select Another Product</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_product_3</t>
+          <t>select_product_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select Another Product</t>
+          <t>10. Select Product</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_product_4</t>
+          <t>select_product_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select Product</t>
+          <t>11. Select Another Product</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +773,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_product_5</t>
+          <t>select_product_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select Another Product</t>
+          <t>12. Select Product</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_product_6</t>
+          <t>select_product_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Select Product</t>
+          <t>13. Select Another Product</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_product_7</t>
+          <t>select_product_8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Product</t>
+          <t>14. Select Another Product</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>select_product_8</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Select Product</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>select_product_9</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>select_product_10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>select_product_11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>select_product_12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_product_13</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_product_14</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select Product</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>select_product_15</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_product_16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_product_17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_product_18</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Select Another Product</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,10 +845,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_product_choices</t>
+          <t>product_select_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +890,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_product_choices</t>
+          <t>product_select_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +907,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_product_choices</t>
+          <t>product_select_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1420,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>organic_celery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Organic Celery</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1184,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>organic_kale</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Organic Kale</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_product_8_choices</t>
+          <t>select_product_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>organic_avocado</t>
+          <t>organic_tomatoes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Organic Avocado</t>
+          <t>Organic Tomatoes</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>organic_strawberries</t>
+          <t>organic_avocado</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Organic Strawberries</t>
+          <t>Organic Avocado</t>
         </is>
       </c>
     </row>
@@ -1488,233 +1235,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>organic_pears</t>
+          <t>organic_strawberries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Organic Pears</t>
+          <t>Organic Strawberries</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_product_9_choices</t>
+          <t>select_product_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>organic_celery</t>
+          <t>organic_pears</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Organic Celery</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_product_9_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>organic_kale</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Organic Kale</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_product_9_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>organic_tomatoes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Organic Tomatoes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_product_10_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>organic_pineapple</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Organic Pineapple</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_product_10_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>organic_watermelon</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Organic Watermelon</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_product_10_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>organic_blueberries</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Organic Blueberries</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_product_11_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_product_11_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_product_12_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>organic_pumpkin</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Organic Pumpkin</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_product_12_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>organic_squash</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Organic Squash</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_product_12_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>organic_cucumber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Organic Cucumber</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>select_product_13_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_product_13_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Organic Pears</t>
         </is>
       </c>
     </row>
